--- a/cases/03_模板示例/示例数据.xlsx
+++ b/cases/03_模板示例/示例数据.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销售明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户信息" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品目录" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基站明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="站点信息" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="频段目录" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地理坐标" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度业绩" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度指标" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,19 +461,21 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>订单ID</t>
+          <t>基站ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -493,40 +495,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>产品编码</t>
+          <t>频段</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>产品名</t>
+          <t>带宽(MHz)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>产品类别</t>
+          <t>覆盖类型</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>基站类型</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>连接用户数</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>客户ID</t>
+          <t>上行PRB利用率</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>销售员</t>
+          <t>下行PRB利用率</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>下行速率(Mbps)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>站点ID</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>季度</t>
         </is>
@@ -535,56 +547,60 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ORD1001</t>
+          <t>C100001</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-01-07</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>P005</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>智能手表</t>
-        </is>
+          <t>n28</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>穿戴设备</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>36660.19</v>
+          <t>微站</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>C012</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>张伟</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
+        <v>158</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>917.9</v>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>S5032</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
@@ -593,56 +609,60 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ORD1002</t>
+          <t>C100002</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2024-01-20</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华西</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>西安</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>P001</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>5G手机A</t>
-        </is>
+          <t>n41</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>80</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>31606.64</v>
+          <t>宏站</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>C004</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>陈静</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
+        <v>431</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>784.6</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>S5026</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
@@ -651,56 +671,60 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ORD1003</t>
+          <t>C100003</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>P007</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>平板电脑</t>
-        </is>
+          <t>n41</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>80</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>终端</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>61725.91</v>
+          <t>宏站</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>C005</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>张伟</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
+        <v>490</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>992.1</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>S5005</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
@@ -709,56 +733,60 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ORD1004</t>
+          <t>C100004</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2024-01-03</t>
+          <t>2024-02-11</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华西</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>西安</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>P006</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>无线耳机</t>
-        </is>
+          <t>n28</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>30</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>穿戴设备</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>17733.82</v>
+          <t>室内分布</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>C006</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>张伟</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
+        <v>399</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>968.6</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>S5008</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
@@ -767,56 +795,60 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ORD1005</t>
+          <t>C100005</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>华西</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>P006</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>无线耳机</t>
-        </is>
+          <t>n41</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>80</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>穿戴设备</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>25028.32</v>
+          <t>宏站</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>C001</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>刘洋</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
+        <v>306</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>306.4</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>S5020</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
@@ -825,56 +857,60 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ORD1006</t>
+          <t>C100006</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>华西</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>P005</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>智能手表</t>
-        </is>
+          <t>n28</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>30</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>穿戴设备</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>93153.42999999999</v>
+          <t>室内分布</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>C006</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>陈静</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
+        <v>356</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>1129.1</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>S5020</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
@@ -883,56 +919,60 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ORD1007</t>
+          <t>C100007</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>P004</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>路由器Y</t>
-        </is>
+          <t>n41</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>100</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>网络设备</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>34226.09</v>
+          <t>宏站</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>C004</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>张伟</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
+        <v>467</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>965.8</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>S5031</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
@@ -941,56 +981,60 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ORD1008</t>
+          <t>C100008</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>P006</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>无线耳机</t>
-        </is>
+          <t>n79</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>100</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>穿戴设备</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>12959.82</v>
+          <t>室内分布</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>C004</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>王强</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
+        <v>415</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>849.9</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>S5029</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
@@ -999,12 +1043,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ORD1009</t>
+          <t>C100009</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1019,36 +1063,40 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>P004</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>路由器Y</t>
-        </is>
+          <t>n41</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>100</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>网络设备</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>19264.39</v>
+          <t>微站</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>C005</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>陈静</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
+        <v>351</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>207.2</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>S5004</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
@@ -1057,56 +1105,60 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ORD1010</t>
+          <t>C100010</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>P004</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>路由器Y</t>
-        </is>
+          <t>n78</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>80</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>网络设备</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>9925.129999999999</v>
+          <t>宏站</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>C007</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>王强</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
+        <v>192</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>332.3</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>S5031</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
@@ -1115,12 +1167,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ORD1011</t>
+          <t>C100011</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1135,36 +1187,40 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>P004</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>路由器Y</t>
-        </is>
+          <t>n79</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>100</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>网络设备</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>59740.22</v>
+          <t>宏站</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>C011</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>刘洋</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
+        <v>387</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>667</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>S5004</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
@@ -1173,56 +1229,60 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ORD1012</t>
+          <t>C100012</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2024-03-14</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>P004</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>路由器Y</t>
-        </is>
+          <t>n79</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>80</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>网络设备</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>52567.58</v>
+          <t>宏站</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>C012</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>陈静</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
+        <v>148</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>621.9</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>S5030</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
@@ -1231,70 +1291,74 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ORD1013</t>
+          <t>C100013</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>华西</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>西安</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>P004</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>路由器Y</t>
-        </is>
+          <t>n78</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>100</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>网络设备</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>16935.26</v>
+          <t>室内分布</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>C002</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>张伟</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>Q1</t>
+        <v>97</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>366.3</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>S5031</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Q2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ORD1014</t>
+          <t>C100014</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1304,41 +1368,45 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>P007</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>平板电脑</t>
-        </is>
+          <t>n78</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>100</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>终端</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>123282</v>
+          <t>微站</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>C007</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>陈静</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
+        <v>249</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>655</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>S5032</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
@@ -1347,56 +1415,60 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ORD1015</t>
+          <t>C100015</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>P002</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>5G手机B</t>
-        </is>
+          <t>n28</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>30</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>214110.27</v>
+          <t>宏站</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>C005</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>王强</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
+        <v>432</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>676.8</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>S5011</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
@@ -1405,56 +1477,60 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ORD1016</t>
+          <t>C100016</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>P003</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>路由器X</t>
-        </is>
+          <t>n78</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>60</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>网络设备</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>26010.86</v>
+          <t>宏站</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>C012</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>王强</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
+        <v>256</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>446.2</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>S5003</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
@@ -1463,12 +1539,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ORD1017</t>
+          <t>C100017</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1483,36 +1559,40 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>P004</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>路由器Y</t>
-        </is>
+          <t>n28</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>网络设备</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>17498.1</v>
+          <t>宏站</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>C003</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>陈静</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
+        <v>172</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>845.5</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>S5021</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
@@ -1521,7 +1601,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ORD1018</t>
+          <t>C100018</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1536,41 +1616,45 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>P008</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>笔记本电脑</t>
-        </is>
+          <t>n79</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>100</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>终端</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>37104.23</v>
+          <t>宏站</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>C006</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>王强</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
+        <v>309</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>1080.9</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>S5024</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
@@ -1579,56 +1663,60 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ORD1019</t>
+          <t>C100019</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>P002</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>5G手机B</t>
-        </is>
+          <t>n28</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>30</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>42772.2</v>
+          <t>室内分布</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>C002</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>陈静</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
+        <v>389</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>464.5</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>S5010</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
@@ -1637,56 +1725,60 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ORD1020</t>
+          <t>C100020</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>P003</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>路由器X</t>
-        </is>
+          <t>n41</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>80</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>网络设备</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>19035.74</v>
+          <t>宏站</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>C010</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>刘洋</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
+        <v>308</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>1046.1</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>S5028</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
@@ -1695,56 +1787,60 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ORD1021</t>
+          <t>C100021</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>P007</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>平板电脑</t>
-        </is>
+          <t>n78</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>80</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>终端</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>162024.71</v>
+          <t>宏站</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>C008</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>陈静</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
+        <v>132</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>627.7</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>S5008</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
@@ -1753,12 +1849,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ORD1022</t>
+          <t>C100022</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1773,36 +1869,40 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>P004</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>路由器Y</t>
-        </is>
+          <t>n78</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>80</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>网络设备</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>11123.12</v>
+          <t>室内分布</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>C010</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>陈静</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
+        <v>270</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>1099</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>S5003</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
@@ -1811,12 +1911,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ORD1023</t>
+          <t>C100023</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1831,36 +1931,40 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>P002</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>5G手机B</t>
-        </is>
+          <t>n78</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>80</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>207814.21</v>
+          <t>室内分布</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>C004</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>张伟</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
+        <v>367</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>436.7</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>S5012</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
@@ -1869,56 +1973,60 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>ORD1024</t>
+          <t>C100024</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华西</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>P004</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>路由器Y</t>
-        </is>
+          <t>n41</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>80</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>网络设备</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>30026.71</v>
+          <t>微站</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>C004</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>陈静</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
+        <v>186</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>582.5</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>S5031</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
@@ -1927,56 +2035,60 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ORD1025</t>
+          <t>C100025</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>华西</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>P008</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>笔记本电脑</t>
-        </is>
+          <t>n79</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>80</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>终端</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>196817.56</v>
+          <t>微站</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>C002</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>刘洋</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
+        <v>164</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>528.3</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>S5005</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
@@ -1985,56 +2097,60 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ORD1026</t>
+          <t>C100026</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>华西</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>西安</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>P008</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>笔记本电脑</t>
-        </is>
+          <t>n79</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>80</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>终端</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>58904.11</v>
+          <t>宏站</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>C011</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>张伟</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
+        <v>499</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>1162.5</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>S5003</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
@@ -2043,12 +2159,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ORD1027</t>
+          <t>C100027</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -2063,36 +2179,40 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>P002</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>5G手机B</t>
-        </is>
+          <t>n28</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>72580.00999999999</v>
+          <t>室内分布</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>C009</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>刘洋</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
+        <v>247</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>244.4</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>S5001</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
@@ -2101,12 +2221,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ORD1028</t>
+          <t>C100028</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2121,36 +2241,40 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>P008</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>笔记本电脑</t>
-        </is>
+          <t>n79</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>100</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>终端</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>155706.16</v>
+          <t>室内分布</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>C002</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>刘洋</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
+        <v>369</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>919.8</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>S5020</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
@@ -2159,56 +2283,60 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>ORD1029</t>
+          <t>C100029</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华西</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>西安</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>P001</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>5G手机A</t>
-        </is>
+          <t>n79</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>80</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>67663.33</v>
+          <t>室内分布</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>C004</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>李娜</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
+        <v>148</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>877.3</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>S5020</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
@@ -2217,56 +2345,60 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ORD1030</t>
+          <t>C100030</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>华西</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>西安</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>P004</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>路由器Y</t>
-        </is>
+          <t>n28</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>30</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>网络设备</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>43674.96</v>
+          <t>微站</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>C003</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>刘洋</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
+        <v>288</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>711.2</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>S5011</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
@@ -2275,56 +2407,60 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>ORD1031</t>
+          <t>C100031</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>华西</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>西安</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>P008</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>笔记本电脑</t>
-        </is>
+          <t>n28</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>30</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>终端</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>157258.79</v>
+          <t>宏站</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>C012</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>陈静</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
+        <v>165</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>246.2</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>S5005</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
@@ -2333,12 +2469,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>ORD1032</t>
+          <t>C100032</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2348,41 +2484,45 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>西安</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>P004</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>路由器Y</t>
-        </is>
+          <t>n41</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>80</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>网络设备</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>27346.72</v>
+          <t>微站</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>C001</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>陈静</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
+        <v>174</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>1092.7</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>S5007</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
@@ -2391,56 +2531,60 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ORD1033</t>
+          <t>C100033</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华西</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>P001</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>5G手机A</t>
-        </is>
+          <t>n41</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>80</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>49203.96</v>
+          <t>宏站</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>C009</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>陈静</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
+        <v>484</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>664.6</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>S5021</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
@@ -2449,230 +2593,246 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ORD1034</t>
+          <t>C100034</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华西</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>西安</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>P003</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>路由器X</t>
-        </is>
+          <t>n41</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>80</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>网络设备</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>8321.68</v>
+          <t>微站</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>C011</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>李娜</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>Q3</t>
+        <v>434</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>965.8</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>S5032</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Q4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>ORD1035</t>
+          <t>C100035</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>P001</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>5G手机A</t>
-        </is>
+          <t>n79</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>100</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>230854.6</v>
+          <t>室内分布</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>C011</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>陈静</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>Q3</t>
+        <v>170</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>740.2</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>S5010</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Q4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>ORD1036</t>
+          <t>C100036</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>P004</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>路由器Y</t>
-        </is>
+          <t>n41</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>100</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>网络设备</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>65012.75</v>
+          <t>宏站</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>C004</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>王强</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>Q3</t>
+        <v>258</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>262.3</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>S5027</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Q4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ORD1037</t>
+          <t>C100037</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华西</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>P006</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>无线耳机</t>
-        </is>
+          <t>n79</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>80</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>穿戴设备</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>6899.96</v>
+          <t>宏站</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>C010</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>陈静</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
+        <v>202</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>1153.4</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>S5015</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
@@ -2681,56 +2841,60 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>ORD1038</t>
+          <t>C100038</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>P005</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>智能手表</t>
-        </is>
+          <t>n79</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>80</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>穿戴设备</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>29364.73</v>
+          <t>宏站</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>C002</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>李娜</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
+        <v>222</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>924.2</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>S5030</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
@@ -2739,56 +2903,60 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ORD1039</t>
+          <t>C100039</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>P008</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>笔记本电脑</t>
-        </is>
+          <t>n79</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>100</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>终端</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>289628.54</v>
+          <t>宏站</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>C010</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>陈静</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
+        <v>119</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>460.2</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>S5014</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
@@ -2797,56 +2965,60 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ORD1040</t>
+          <t>C100040</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-02</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华西</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>西安</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>P003</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>路由器X</t>
-        </is>
+          <t>n28</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>网络设备</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>16700.9</v>
+          <t>微站</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>C002</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>陈静</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
+        <v>179</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>949</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>S5023</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
@@ -2855,56 +3027,60 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ORD1041</t>
+          <t>C100041</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>P004</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>路由器Y</t>
-        </is>
+          <t>n78</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>100</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>网络设备</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>61888.52</v>
+          <t>宏站</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>C011</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>王强</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
+        <v>479</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>326.2</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>S5008</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
@@ -2913,56 +3089,60 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ORD1042</t>
+          <t>C100042</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>华西</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>西安</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>P001</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>5G手机A</t>
-        </is>
+          <t>n28</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>62406.72</v>
+          <t>宏站</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>C005</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>张伟</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
+        <v>448</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>308.1</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>S5020</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
@@ -2971,56 +3151,60 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ORD1043</t>
+          <t>C100043</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华西</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>西安</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>P005</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>智能手表</t>
-        </is>
+          <t>n41</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>100</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>穿戴设备</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>32154.99</v>
+          <t>室内分布</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>C009</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>刘洋</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
+        <v>102</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>884.3</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>S5008</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
@@ -3029,12 +3213,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ORD1044</t>
+          <t>C100044</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -3044,41 +3228,45 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>P002</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>5G手机B</t>
-        </is>
+          <t>n79</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>80</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>219696.06</v>
+          <t>宏站</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
       </c>
       <c r="I45" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>C009</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>张伟</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
+        <v>56</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>305.5</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>S5030</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
@@ -3087,12 +3275,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ORD1045</t>
+          <t>C100045</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>2024-12-07</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -3107,36 +3295,40 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>P003</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>路由器X</t>
-        </is>
+          <t>n41</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>80</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>网络设备</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="n">
-        <v>5931.01</v>
+          <t>室内分布</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>C001</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>王强</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
+        <v>288</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>468.4</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>S5016</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
@@ -3145,172 +3337,60 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>ORD1046</t>
+          <t>C100046</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>2024-12-24</t>
+          <t>2024-12-07</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>P006</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>无线耳机</t>
-        </is>
+          <t>n79</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>100</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>穿戴设备</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="n">
-        <v>40104.05</v>
+          <t>微站</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>C007</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>陈静</t>
-        </is>
-      </c>
-      <c r="L47" s="3" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>ORD1047</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>2024-12-24</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>华东</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>P003</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>路由器X</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>网络设备</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="n">
-        <v>16029.89</v>
-      </c>
-      <c r="I48" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>C001</t>
-        </is>
-      </c>
-      <c r="K48" s="3" t="inlineStr">
-        <is>
-          <t>李娜</t>
-        </is>
-      </c>
-      <c r="L48" s="3" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>ORD1048</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>2024-12-13</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>华南</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>P004</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>路由器Y</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>网络设备</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="n">
-        <v>25656.17</v>
-      </c>
-      <c r="I49" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>C012</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>张伟</t>
-        </is>
-      </c>
-      <c r="L49" s="3" t="inlineStr">
+        <v>222</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>381.8</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>S5023</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
@@ -3327,7 +3407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3335,356 +3415,934 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>客户ID</t>
+          <t>站点ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>客户名</t>
+          <t>站点名称</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>行业</t>
+          <t>经度</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>规模</t>
+          <t>纬度</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>城市</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>场景</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C001</t>
+          <t>S5001</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>通达科技</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>互联网</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>大型</t>
-        </is>
+          <t>北京城区站5001</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>116.8366</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>29.1</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>北京</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>城区</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>C002</t>
+          <t>S5002</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>恒泰贸易</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>零售</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>中型</t>
-        </is>
+          <t>北京郊区站5002</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>114.6502</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>29.8928</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>郊区</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C003</t>
+          <t>S5003</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>南方电网</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>能源</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>大型</t>
-        </is>
+          <t>北京高校站5003</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>117.4188</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>31.7068</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>高校</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>C004</t>
+          <t>S5004</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>西部物流</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>物流</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>中型</t>
-        </is>
+          <t>北京交通枢纽站5004</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>118.3531</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>29.3478</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>交通枢纽</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>C005</t>
+          <t>S5005</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>京东数码</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>零售</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>大型</t>
-        </is>
+          <t>天津城区站5005</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>115.5315</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>29.1192</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>城区</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>C006</t>
+          <t>S5006</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>阿里云</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>互联网</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>大型</t>
-        </is>
+          <t>天津郊区站5006</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>114.3118</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>31.0214</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>郊区</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>C007</t>
+          <t>S5007</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>腾讯科技</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>互联网</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>大型</t>
-        </is>
+          <t>天津高校站5007</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>113.1592</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>29.7954</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>高校</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>C008</t>
+          <t>S5008</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>美的集团</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>制造</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>大型</t>
-        </is>
+          <t>天津交通枢纽站5008</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>116.8993</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>31.1798</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>交通枢纽</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>C009</t>
+          <t>S5009</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>长安汽车</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>制造</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>中型</t>
-        </is>
+          <t>上海城区站5009</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>119.3226</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>31.3571</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>城区</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>C010</t>
+          <t>S5010</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>海尔智家</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>制造</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>大型</t>
-        </is>
+          <t>上海郊区站5010</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>122.8566</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>29.026</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>郊区</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>C011</t>
+          <t>S5011</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>网易</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>互联网</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>中型</t>
-        </is>
+          <t>上海高校站5011</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>122.8349</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>31.7926</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>高校</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>C012</t>
+          <t>S5012</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>顺丰速运</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>物流</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>大型</t>
-        </is>
+          <t>上海交通枢纽站5012</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>120.0415</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>29.6219</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>交通枢纽</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>S5013</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>杭州城区站5013</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>118.7433</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>30.3464</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>城区</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>S5014</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>杭州郊区站5014</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>113.5565</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>29.3869</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>郊区</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>S5015</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>杭州高校站5015</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>118.085</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>31.4149</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>高校</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>S5016</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>杭州交通枢纽站5016</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>117.8428</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>31.9189</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>交通枢纽</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>S5017</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>广州城区站5017</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>116.2174</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>32.8925</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>城区</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>S5018</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>广州郊区站5018</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>115.2712</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>31.2082</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>郊区</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>S5019</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>广州高校站5019</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>117.9764</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>31.4741</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>高校</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>S5020</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>广州交通枢纽站5020</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>118.1702</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>31.3094</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>交通枢纽</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>S5021</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>深圳城区站5021</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>117.2274</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>29.1833</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>城区</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>S5022</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>深圳郊区站5022</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>114.3674</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>30.1576</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>郊区</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>S5023</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>深圳高校站5023</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>113.4788</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>29.9312</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>高校</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>S5024</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>深圳交通枢纽站5024</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>113.606</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>30.1119</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>交通枢纽</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>S5025</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>成都城区站5025</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>116.8141</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>30.4593</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>城区</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>S5026</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>成都郊区站5026</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>115.2211</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>29.838</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>郊区</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>S5027</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>成都高校站5027</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>114.6019</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>32.7466</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>高校</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>S5028</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>成都交通枢纽站5028</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>116.8882</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>31.4365</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>交通枢纽</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>S5029</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>西安城区站5029</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>114.0268</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>31.9165</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
           <t>西安</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>城区</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>S5030</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>西安郊区站5030</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>113.9804</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>30.5178</v>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>郊区</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>S5031</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>西安高校站5031</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>118.9371</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>31.56</v>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>高校</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>S5032</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>西安交通枢纽站5032</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>116.3417</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>31.7385</v>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>交通枢纽</t>
         </is>
       </c>
     </row>
@@ -3699,7 +4357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3711,183 +4369,103 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>产品编码</t>
+          <t>频段</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>产品名</t>
+          <t>频段名称</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>产品类别</t>
+          <t>频带</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>单价</t>
+          <t>最大带宽</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P001</t>
+          <t>n78</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>5G手机A</t>
+          <t>3.5GHz</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>C-Band</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>5999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>n41</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>5G手机B</t>
+          <t>2.6GHz</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>C-Band</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>3999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>n28</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>路由器X</t>
+          <t>700MHz</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>网络设备</t>
+          <t>低频</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>899</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>n79</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>路由器Y</t>
+          <t>4.9GHz</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>网络设备</t>
+          <t>C-Band</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>P005</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>智能手表</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>穿戴设备</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>P006</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>无线耳机</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>穿戴设备</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>P007</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>平板电脑</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>终端</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>3299</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>P008</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>笔记本电脑</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>终端</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>6999</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -3934,7 +4512,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>基站数</t>
         </is>
       </c>
     </row>
@@ -3956,7 +4534,7 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>761672</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -3977,7 +4555,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>135413</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -3998,7 +4576,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>387230</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -4019,7 +4597,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>420172</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -4040,7 +4618,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>645114</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -4061,7 +4639,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>198428</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -4082,7 +4660,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>342346</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -4103,7 +4681,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>411760</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4121,10 +4699,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4135,22 +4713,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>销售额</t>
+          <t>连接用户数</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>成本</t>
+          <t>流量(TB)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>利润</t>
+          <t>下行PRB利用率</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>订单数</t>
+          <t>下行速率(Mbps)</t>
         </is>
       </c>
     </row>
@@ -4161,16 +4739,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>172754.88</v>
+        <v>1079</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>112290.67</v>
+        <v>775.3</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>60464.21</v>
+        <v>56.6</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>94</v>
+        <v>898.2</v>
       </c>
     </row>
     <row r="3">
@@ -4180,16 +4758,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>140339.34</v>
+        <v>1528</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>91220.57000000001</v>
+        <v>1029.9</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>49118.77</v>
+        <v>58.1</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>83</v>
+        <v>842.5</v>
       </c>
     </row>
     <row r="4">
@@ -4199,16 +4777,16 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>158432.58</v>
+        <v>1493</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>102981.18</v>
+        <v>639.8</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>55451.4</v>
+        <v>59.7</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>121</v>
+        <v>535.7</v>
       </c>
     </row>
     <row r="5">
@@ -4218,16 +4796,16 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>363403.13</v>
+        <v>778</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>236212.03</v>
+        <v>352.3</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>127191.1</v>
+        <v>61.5</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>125</v>
+        <v>566</v>
       </c>
     </row>
     <row r="6">
@@ -4237,16 +4815,16 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>97374.53</v>
+        <v>737</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>63293.44</v>
+        <v>466.3</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>34081.09</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>30</v>
+        <v>790.9</v>
       </c>
     </row>
     <row r="7">
@@ -4256,16 +4834,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>192183.57</v>
+        <v>1099</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>124919.32</v>
+        <v>711.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>67264.25</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>77</v>
+        <v>809.3</v>
       </c>
     </row>
     <row r="8">
@@ -4275,16 +4853,16 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>566142.6</v>
+        <v>1216</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>367992.69</v>
+        <v>659.1</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>198149.91</v>
+        <v>57.5</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>131</v>
+        <v>677.5</v>
       </c>
     </row>
     <row r="9">
@@ -4294,16 +4872,16 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>424303.24</v>
+        <v>764</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>275797.11</v>
+        <v>415.9</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>148506.13</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>83</v>
+        <v>680.5</v>
       </c>
     </row>
     <row r="10">
@@ -4313,16 +4891,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>380739.71</v>
+        <v>1111</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>247480.81</v>
+        <v>603.2</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>133258.9</v>
+        <v>51.7</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>131</v>
+        <v>678.7</v>
       </c>
     </row>
     <row r="11">
@@ -4332,16 +4910,16 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>325893.23</v>
+        <v>1064</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>211830.6</v>
+        <v>664.3</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>114062.63</v>
+        <v>62</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>61</v>
+        <v>780.4</v>
       </c>
     </row>
     <row r="12">
@@ -4351,16 +4929,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>392847.19</v>
+        <v>999</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>255350.67</v>
+        <v>531.4</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>137496.52</v>
+        <v>51.1</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>145</v>
+        <v>664.9</v>
       </c>
     </row>
     <row r="13">
@@ -4370,16 +4948,16 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>87721.12</v>
+        <v>1116</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>57018.73</v>
+        <v>419.3</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>30702.39</v>
+        <v>72.7</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>85</v>
+        <v>469.6</v>
       </c>
     </row>
   </sheetData>
